--- a/Data/Level.xlsx
+++ b/Data/Level.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoldenMansion\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\8\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CEBC43-CB4A-4632-925D-6547205B3159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BF8481B-EF8B-4005-846D-095303D856D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3255" yWindow="1560" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Level" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -389,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -438,7 +449,7 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -449,7 +460,7 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -457,10 +468,10 @@
         <v>3</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -468,10 +479,10 @@
         <v>4</v>
       </c>
       <c r="B8">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -479,14 +490,47 @@
         <v>5</v>
       </c>
       <c r="B9">
+        <v>20</v>
+      </c>
+      <c r="C9">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10">
         <v>25</v>
       </c>
-      <c r="C9">
-        <v>17</v>
+      <c r="C10">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>30</v>
+      </c>
+      <c r="C11">
+        <v>50000</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>35</v>
+      </c>
+      <c r="C12">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>9</v>
       </c>
     </row>
